--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Capucine dit : maman, je peux. Avant de goûter l'inconnu, il faut demander. Capucine va demander à l'adulte. Maman prend le pot. Maman dit : c'est de la confiture. Tu peux goûter. Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Elle dit : maman, je demande. Maman ouvre. Maman dit : ce sont des craquelins. Tu peux en prendre un. Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
+          <t>Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Maman, je peux. Avant de goûter l'inconnu, il faut demander. Capucine va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman.
+enfant-f|Maman, je peux. Avant de goûter l'inconnu, il faut demander.
+narrateur|Capucine va demander à l'adulte. Maman prend le pot.
+maman|C'est de la confiture. Tu peux goûter.
+narrateur|Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman.
+narrateur|Maman, je demande. Maman ouvre.
+maman|Ce sont des craquelins. Tu peux en prendre un.
+narrateur|Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1501,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Capucine voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1678,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Capucine a demandé. L'adulte a répondu. En cuisine, puis au jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1845,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Capucine boit une gorgée d'eau. Maman range le pot.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2012,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2052,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1508,6 +1518,7 @@
           <t>narrateur|Capucine voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1694,7 @@
           <t>narrateur|Capucine a demandé. L'adulte a répondu. En cuisine, puis au jardin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1850,6 +1862,7 @@
           <t>narrateur|Capucine boit une gorgée d'eau. Maman range le pot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2017,6 +2030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2059,6 +2073,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2260,6 +2288,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capucine demande à maman</t>
+          <t>Les deux demandes de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La fenêtre est embuée. Sarah demande pour un pot fermé : c'est de la confiture. Plus tard, au jardin, elle demande pour une boîte : ce sont des craquelins.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Maman, je peux. Avant de goûter l'inconnu, il faut demander. Capucine va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
+          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Tu as fait du bon travail. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman.
-enfant-f|Maman, je peux. Avant de goûter l'inconnu, il faut demander.
-narrateur|Capucine va demander à l'adulte. Maman prend le pot.
-maman|C'est de la confiture. Tu peux goûter.
-narrateur|Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman.
-narrateur|Maman, je demande. Maman ouvre.
-maman|Ce sont des craquelins. Tu peux en prendre un.
-narrateur|Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.</t>
+          <t>narrateur|La fenêtre de la cuisine est toute embuée.
+narrateur|Sarah dessine un petit rond du doigt.
+narrateur|Ça sent le fruit cuit.
+narrateur|Une mouche se pose sur le carreau, puis s'en va.
+maman|Sarah, tu as vu ton rond ?
+enfant-f|Oui, maman. Il est tout flou.
+maman|Il est flou, et il brille.
+narrateur|La maison sent le fruit cuit.
+narrateur|Un torchon rayé pend près de l'évier.
+maman|Tu as senti la cuisine ?
+enfant-f|Oui. Ça sent le fruit.
+maman|Oui. Le fruit cuit.
+narrateur|Maman range des pots.
+narrateur|Les couvercles font un petit clic.
+narrateur|En ce moment, Sarah est près de la table.
+narrateur|Un petit pot fermé est là.
+narrateur|Sarah ne le connaît pas.
+narrateur|C'est de l'inconnu.
+narrateur|Elle a envie de goûter.
+narrateur|Elle pose les mains sur ses genoux.
+narrateur|Elle va vers maman.
+enfant-f|Maman, je peux ?
+maman|Tu demandes. C'est bien.
+narrateur|Avant de goûter l'inconnu, il faut demander.
+narrateur|Sarah va demander à l'adulte.
+narrateur|Maman prend le pot.
+maman|C'est de la confiture.
+maman|Tu peux goûter.
+narrateur|Sarah goûte une petite cuillère.
+narrateur|C'est sucré.
+enfant-f|C'est sucré, maman.
+maman|Oui. Parce que tu as demandé.
+maman|Bravo, Sarah.
+narrateur|Plus tard, elles vont au jardin.
+narrateur|Le banc est encore un peu humide.
+narrateur|Une petite boîte fermée est sur le banc.
+narrateur|Sarah ne la connaît pas.
+narrateur|C'est encore de l'inconnu.
+narrateur|Elle pose les mains sur ses genoux.
+narrateur|Elle va vers maman.
+enfant-f|Maman, je demande.
+maman|Oui. On demande à un adulte.
+narrateur|Maman ouvre.
+maman|Ce sont des craquelins.
+maman|Tu peux en prendre un.
+narrateur|Sarah croque.
+narrateur|C'est croustillant.
+enfant-f|Ça croque, maman.
+maman|Oui. En cuisine, puis au jardin, c'est pareil.
+maman|On demande à un adulte.
+maman|Tu as fait du bon travail.
+narrateur|Maman range la boîte.
+narrateur|Le rond sur la fenêtre a déjà disparu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Capucine voit un pot inconnu. Que fait-elle ?</t>
+          <t>Sarah voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1515,10 +1572,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Capucine voit un pot inconnu. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah voit un pot inconnu.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1543,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Capucine a demandé. L'adulte a répondu. En cuisine, puis au jardin.</t>
+          <t>Sarah a demandé. L'adulte a répondu. En cuisine, puis au jardin. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. La confiture était sucrée. Le craquelin était croustillant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1691,10 +1748,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Capucine a demandé. L'adulte a répondu. En cuisine, puis au jardin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a demandé.
+narrateur|L'adulte a répondu.
+narrateur|En cuisine, puis au jardin.
+maman|Tu as demandé à maman ?
+enfant-f|Oui.
+maman|Bravo.
+maman|On demande à un adulte.
+narrateur|La confiture était sucrée.
+narrateur|Le craquelin était croustillant.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1719,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Capucine boit une gorgée d'eau. Maman range le pot.</t>
+          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1859,10 +1923,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Capucine boit une gorgée d'eau. Maman range le pot.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah boit une gorgée d'eau.
+narrateur|L'eau est fraîche.
+maman|Le pot est rangé ?
+enfant-f|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Maman range le pot.
+narrateur|Le banc du jardin sèche au soleil.
+narrateur|La fenêtre n'est plus embuée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1887,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2027,10 +2097,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah a demandé deux fois.
+narrateur|Une fois pour le pot.
+narrateur|Une fois pour la boîte.
+maman|Bravo, Sarah.
+enfant-f|J'ai demandé.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2049,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2087,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Tu as fait du bon travail. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
+          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Capucine est dans la cuisine. Maman range des pots. Un petit pot fermé est sur la table. Capucine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Capucine dit : maman, je peux. Avant de goûter l'inconnu, il faut &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Capucine va demander à l'adulte. Maman prend le pot. Maman dit : c'est de la confiture. Tu peux goûter. Capucine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Plus tard, elles vont au jardin. Une petite boîte fermée est sur le banc. Capucine ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Elle dit : maman, je demande. Maman ouvre. Maman dit : ce sont des craquelins. Tu peux en prendre un. Capucine croque. C'est croustillant. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Capucine sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,7 +1374,6 @@
 enfant-f|Ça croque, maman.
 maman|Oui. En cuisine, puis au jardin, c'est pareil.
 maman|On demande à un adulte.
-maman|Tu as fait du bon travail.
 narrateur|Maman range la boîte.
 narrateur|Le rond sur la fenêtre a déjà disparu.</t>
         </is>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Capucine voit un pot &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1605,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Capucine a demandé. L'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt; a répondu. En cuisine, puis au jardin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a demandé. L'adulte a répondu. En cuisine, puis au jardin. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. La confiture était sucrée. Le craquelin était croustillant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1783,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
+          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Capucine boit une gorgée d'eau. Maman range le pot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1926,6 @@
 narrateur|L'eau est fraîche.
 maman|Le pot est rangé ?
 enfant-f|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|Maman range le pot.
 narrateur|Le banc du jardin sèche au soleil.
 narrateur|La fenêtre n'est plus embuée.</t>
@@ -1957,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé. L'histoire est finie.</t>
+          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,8 +2099,7 @@
 narrateur|Une fois pour le pot.
 narrateur|Une fois pour la boîte.
 maman|Bravo, Sarah.
-enfant-f|J'ai demandé.
-narrateur|L'histoire est finie.</t>
+enfant-f|J'ai demandé.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capucine, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les deux demandes de Sarah</t>
+          <t>Le pot sans nom</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine puis jardin</t>
+          <t>cuisine de village, pluie sur le zinc, pain tiède</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La fenêtre est embuée. Sarah demande pour un pot fermé : c'est de la confiture. Plus tard, au jardin, elle demande pour une boîte : ce sont des craquelins.</t>
+          <t>Sarah veut du pain tiède avec quelque chose de doux. Un pot fermé n'a pas de nom. Elle tend la main. La main de maman attend. Sarah dit je peux. Elles goûtent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
+          <t>La pluie chante sur le zinc. La vitre de la cuisine est toute embuée. Ça sent le pain qui sort du four. Un torchon rayé pend près de l'évier. Une miche dorée attend sur la planche. Tu as vu la buée, Sarah ? Je fais un rond, maman. Le doigt dessine un petit hublot. Derrière, un toit luisant dégoutte. Je veux du pain. Avec quelque chose de doux. La miche est encore chaude. On va lui trouver un ami ? Oui. En ce moment, Sarah s'approche de la table. Un petit pot brun est là, fermé. Le couvercle n'a pas de dessin. Le verre est opaque, un peu gras. Qu'est-ce que c'est ? Sarah tend les doigts vers le verre. La main de maman s'arrête à côté. Elle n'attrape pas. Elle attend, ouverte, tout près. Les doigts de Sarah s'arrêtent aussi. Maman, je peux ? Oui. On ouvre ensemble. Le couvercle fait un petit clic. Une odeur de figue monte, épaisse. Ça sent le fruit. C'est de la confiture. Tu goûtes avec moi ? Oui. Deux cuillères trempent, toutes petites. Sarah goûte. C'est sucré. Et un peu de pépins. Des figues. Merci, Sarah. Tu as attendu ma main. Maman coupe une tranche tiède. La confiture glisse, sombre, sur le pain. Pour moi ? Pour toi. Sarah croque. Le pain craque, la figue colle. C'est bon. Le zinc chante encore ? Oui. Une goutte court sur le hublot du doigt. Le pot reste ouvert, entre elles deux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre de la cuisine est toute embuée. Sarah dessine un petit rond du doigt. Ça sent le fruit cuit. Une mouche se pose sur le carreau, puis s'en va. Sarah, tu as vu ton rond ? Oui, maman. Il est tout flou. Il est flou, et il brille. La maison sent le fruit cuit. Un torchon rayé pend près de l'évier. Tu as senti la cuisine ? Oui. Ça sent le fruit. Oui. Le fruit cuit. Maman range des pots. Les couvercles font un petit clic. En ce moment, Sarah est près de la table. Un petit pot fermé est là. Sarah ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Sarah va demander à l'adulte. Maman prend le pot. C'est de la confiture. Tu peux goûter. Sarah goûte une petite cuillère. C'est sucré. C'est sucré, maman. Oui. Parce que tu as demandé. Bravo, Sarah. Plus tard, elles vont au jardin. Le banc est encore un peu humide. Une petite boîte fermée est sur le banc. Sarah ne la connaît pas. C'est encore de l'inconnu. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je demande. Oui. On demande à un adulte. Maman ouvre. Ce sont des craquelins. Tu peux en prendre un. Sarah croque. C'est croustillant. Ça croque, maman. Oui. En cuisine, puis au jardin, c'est pareil. On demande à un adulte. Maman range la boîte. Le rond sur la fenêtre a déjà disparu.</t>
+          <t>La pluie chante sur le zinc. La vitre de la cuisine est toute embuée. Ça sent le pain qui sort du four. Un torchon rayé pend près de l'évier. Une miche dorée attend sur la planche. Tu as vu la buée, Sarah ? Je fais un rond, maman. Le doigt dessine un petit hublot. Derrière, un toit luisant dégoutte. Je veux du pain. Avec quelque chose de doux. La miche est encore chaude. On va lui trouver un ami ? Oui. En ce moment, Sarah s'approche de la table. Un petit pot brun est là, fermé. Le couvercle n'a pas de dessin. Le verre est opaque, un peu gras. Qu'est-ce que c'est ? Sarah tend les doigts vers le verre. La main de maman s'arrête à côté. Elle n'attrape pas. Elle attend, ouverte, tout près. Les doigts de Sarah s'arrêtent aussi. Maman, je peux ? Oui. On ouvre ensemble. Le couvercle fait un petit clic. Une odeur de figue monte, épaisse. Ça sent le fruit. C'est de la confiture. Tu goûtes avec moi ? Oui. Deux cuillères trempent, toutes petites. Sarah goûte. C'est sucré. Et un peu de pépins. Des figues. Merci, Sarah. Tu as attendu ma main. Maman coupe une tranche tiède. La confiture glisse, sombre, sur le pain. Pour moi ? Pour toi. Sarah croque. Le pain craque, la figue colle. C'est bon. Le zinc chante encore ? Oui. Une goutte court sur le hublot du doigt. Le pot reste ouvert, entre elles deux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,58 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La fenêtre de la cuisine est toute embuée.
-narrateur|Sarah dessine un petit rond du doigt.
-narrateur|Ça sent le fruit cuit.
-narrateur|Une mouche se pose sur le carreau, puis s'en va.
-maman|Sarah, tu as vu ton rond ?
-enfant-f|Oui, maman. Il est tout flou.
-maman|Il est flou, et il brille.
-narrateur|La maison sent le fruit cuit.
+          <t>narrateur|La pluie chante sur le zinc.
+narrateur|La vitre de la cuisine est toute embuée.
+narrateur|Ça sent le pain qui sort du four.
 narrateur|Un torchon rayé pend près de l'évier.
-maman|Tu as senti la cuisine ?
-enfant-f|Oui. Ça sent le fruit.
-maman|Oui. Le fruit cuit.
-narrateur|Maman range des pots.
-narrateur|Les couvercles font un petit clic.
-narrateur|En ce moment, Sarah est près de la table.
-narrateur|Un petit pot fermé est là.
-narrateur|Sarah ne le connaît pas.
-narrateur|C'est de l'inconnu.
-narrateur|Elle a envie de goûter.
-narrateur|Elle pose les mains sur ses genoux.
-narrateur|Elle va vers maman.
+narrateur|Une miche dorée attend sur la planche.
+maman|Tu as vu la buée, Sarah ?
+enfant-f|Je fais un rond, maman.
+narrateur|Le doigt dessine un petit hublot.
+narrateur|Derrière, un toit luisant dégoutte.
+enfant-f|Je veux du pain.
+enfant-f|Avec quelque chose de doux.
+maman|La miche est encore chaude.
+maman|On va lui trouver un ami ?
+enfant-f|Oui.
+narrateur|En ce moment, Sarah s'approche de la table.
+narrateur|Un petit pot brun est là, fermé.
+narrateur|Le couvercle n'a pas de dessin.
+narrateur|Le verre est opaque, un peu gras.
+enfant-f|Qu'est-ce que c'est ?
+narrateur|Sarah tend les doigts vers le verre.
+narrateur|La main de maman s'arrête à côté.
+narrateur|Elle n'attrape pas.
+narrateur|Elle attend, ouverte, tout près.
+narrateur|Les doigts de Sarah s'arrêtent aussi.
 enfant-f|Maman, je peux ?
-maman|Tu demandes. C'est bien.
-narrateur|Avant de goûter l'inconnu, il faut demander.
-narrateur|Sarah va demander à l'adulte.
-narrateur|Maman prend le pot.
+maman|Oui.
+maman|On ouvre ensemble.
+narrateur|Le couvercle fait un petit clic.
+narrateur|Une odeur de figue monte, épaisse.
+enfant-f|Ça sent le fruit.
 maman|C'est de la confiture.
-maman|Tu peux goûter.
-narrateur|Sarah goûte une petite cuillère.
-narrateur|C'est sucré.
-enfant-f|C'est sucré, maman.
-maman|Oui. Parce que tu as demandé.
-maman|Bravo, Sarah.
-narrateur|Plus tard, elles vont au jardin.
-narrateur|Le banc est encore un peu humide.
-narrateur|Une petite boîte fermée est sur le banc.
-narrateur|Sarah ne la connaît pas.
-narrateur|C'est encore de l'inconnu.
-narrateur|Elle pose les mains sur ses genoux.
-narrateur|Elle va vers maman.
-enfant-f|Maman, je demande.
-maman|Oui. On demande à un adulte.
-narrateur|Maman ouvre.
-maman|Ce sont des craquelins.
-maman|Tu peux en prendre un.
+maman|Tu goûtes avec moi ?
+enfant-f|Oui.
+narrateur|Deux cuillères trempent, toutes petites.
+narrateur|Sarah goûte.
+enfant-f|C'est sucré.
+enfant-f|Et un peu de pépins.
+maman|Des figues.
+maman|Merci, Sarah.
+maman|Tu as attendu ma main.
+narrateur|Maman coupe une tranche tiède.
+narrateur|La confiture glisse, sombre, sur le pain.
+enfant-f|Pour moi ?
+maman|Pour toi.
 narrateur|Sarah croque.
-narrateur|C'est croustillant.
-enfant-f|Ça croque, maman.
-maman|Oui. En cuisine, puis au jardin, c'est pareil.
-maman|On demande à un adulte.
-narrateur|Maman range la boîte.
-narrateur|Le rond sur la fenêtre a déjà disparu.</t>
+narrateur|Le pain craque, la figue colle.
+enfant-f|C'est bon.
+maman|Le zinc chante encore ?
+enfant-f|Oui.
+narrateur|Une goutte court sur le hublot du doigt.
+narrateur|Le pot reste ouvert, entre elles deux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1407,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sarah voit un pot inconnu. Que fait-elle ?</t>
+          <t>Sarah voit un pot fermé. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah voit un pot inconnu. Que fait-elle ?</t>
+          <t>Sarah voit un pot fermé. Que dit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1427,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | à maman | un adulte | elle demande | à l'adulte</t>
+          <t>demander | je peux | à maman | un adulte | elle demande | à l'adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1442,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle va demander. Elle parle à maman. Que fait Capucine ?</t>
+          <t>Sarah parle à maman. Que dit-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1491,7 +1490,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1571,8 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah voit un pot inconnu.
-narrateur|Que fait-elle ?</t>
+          <t>narrateur|Sarah voit un pot fermé.
+narrateur|Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a demandé. L'adulte a répondu. En cuisine, puis au jardin. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. La confiture était sucrée. Le craquelin était croustillant.</t>
+          <t>La tranche a un trou de confiture. Sarah lèche un pépin sur le pouce. Tu veux encore un peu ? Je peux ? Oui. Elles trempent encore la cuillère. Le verre du pot est tiède, maintenant. Il n'avait pas de nom. On ne savait pas. Alors on a ouvert ensemble. La pluie ralentit sur le zinc. Le hublot du doigt s'efface un peu. Le pain est encore chaud. Tu le sens ? Sous les doigts, oui. Des miettes dorées restent sur la planche. Le torchon rayé sent la figue, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a demandé. L'adulte a répondu. En cuisine, puis au jardin. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. La confiture était sucrée. Le craquelin était croustillant.</t>
+          <t>La tranche a un trou de confiture. Sarah lèche un pépin sur le pouce. Tu veux encore un peu ? Je peux ? Oui. Elles trempent encore la cuillère. Le verre du pot est tiède, maintenant. Il n'avait pas de nom. On ne savait pas. Alors on a ouvert ensemble. La pluie ralentit sur le zinc. Le hublot du doigt s'efface un peu. Le pain est encore chaud. Tu le sens ? Sous les doigts, oui. Des miettes dorées restent sur la planche. Le torchon rayé sent la figue, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1660,7 +1659,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1747,15 +1746,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a demandé.
-narrateur|L'adulte a répondu.
-narrateur|En cuisine, puis au jardin.
-maman|Tu as demandé à maman ?
-enfant-f|Oui.
-maman|Bravo.
-maman|On demande à un adulte.
-narrateur|La confiture était sucrée.
-narrateur|Le craquelin était croustillant.</t>
+          <t>narrateur|La tranche a un trou de confiture.
+narrateur|Sarah lèche un pépin sur le pouce.
+maman|Tu veux encore un peu ?
+enfant-f|Je peux ?
+maman|Oui.
+narrateur|Elles trempent encore la cuillère.
+narrateur|Le verre du pot est tiède, maintenant.
+enfant-f|Il n'avait pas de nom.
+maman|On ne savait pas.
+maman|Alors on a ouvert ensemble.
+narrateur|La pluie ralentit sur le zinc.
+narrateur|Le hublot du doigt s'efface un peu.
+enfant-f|Le pain est encore chaud.
+maman|Tu le sens ?
+enfant-f|Sous les doigts, oui.
+narrateur|Des miettes dorées restent sur la planche.
+narrateur|Le torchon rayé sent la figue, maintenant.</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
+          <t>Sarah boit une gorgée d'eau. L'eau lave le sucre de la langue. On referme le pot ? Oui, maman. Le clic du couvercle est doux. C'était des figues. Oui. On le sait, maintenant. La miche a une tranche en moins. Elle sent encore le four. Tu as encore faim ? Non. C'était bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sarah boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le banc du jardin sèche au soleil. La fenêtre n'est plus embuée.</t>
+          <t>Sarah boit une gorgée d'eau. L'eau lave le sucre de la langue. On referme le pot ? Oui, maman. Le clic du couvercle est doux. C'était des figues. Oui. On le sait, maintenant. La miche a une tranche en moins. Elle sent encore le four. Tu as encore faim ? Non. C'était bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1843,7 +1850,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1923,12 +1930,18 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Sarah boit une gorgée d'eau.
-narrateur|L'eau est fraîche.
-maman|Le pot est rangé ?
+narrateur|L'eau lave le sucre de la langue.
+maman|On referme le pot ?
 enfant-f|Oui, maman.
-narrateur|Maman range le pot.
-narrateur|Le banc du jardin sèche au soleil.
-narrateur|La fenêtre n'est plus embuée.</t>
+narrateur|Le clic du couvercle est doux.
+enfant-f|C'était des figues.
+maman|Oui.
+maman|On le sait, maintenant.
+narrateur|La miche a une tranche en moins.
+narrateur|Elle sent encore le four.
+maman|Tu as encore faim ?
+enfant-f|Non.
+enfant-f|C'était bon.</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé.</t>
+          <t>Le pain sent encore la figue. J'ai dit je peux. Oui. Le zinc est calme, presque. Le pot brun reste entre leurs mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sarah a demandé deux fois. Une fois pour le pot. Une fois pour la boîte. Bravo, Sarah. J'ai demandé.</t>
+          <t>Le pain sent encore la figue. J'ai dit je peux. Oui. Le zinc est calme, presque. Le pot brun reste entre leurs mains.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2016,7 +2029,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2095,11 +2108,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a demandé deux fois.
-narrateur|Une fois pour le pot.
-narrateur|Une fois pour la boîte.
-maman|Bravo, Sarah.
-enfant-f|J'ai demandé.</t>
+          <t>narrateur|Le pain sent encore la figue.
+enfant-f|J'ai dit je peux.
+maman|Oui.
+narrateur|Le zinc est calme, presque.
+narrateur|Le pot brun reste entre leurs mains.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2183,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
